--- a/docs/Cost per unit calculation.xlsx
+++ b/docs/Cost per unit calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\QMUL Year 2 modules\Semester 2\EMS501U - Designing for Sustainable Manufacture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\QMUL Year 2 modules\Semester 2\EMS501U - Designing for Sustainable Manufacture\Exam Prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44324671-3E39-4D8F-8F24-73C63A4ADB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B025A23-D3CF-44B6-BB09-18FB29653CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" xr2:uid="{B80BF410-154E-4A60-8685-422C7C147F4D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B80BF410-154E-4A60-8685-422C7C147F4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost per unit calc" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
   <si>
     <t xml:space="preserve">Scrap fraction, f = </t>
   </si>
   <si>
     <t xml:space="preserve">Batch size, n = </t>
-  </si>
-  <si>
-    <t>Rate of production, n_dot =</t>
   </si>
   <si>
     <t>Load factor, L =</t>
@@ -196,9 +193,6 @@
     </r>
   </si>
   <si>
-    <t>Extra: if capital and labour is not ignored</t>
-  </si>
-  <si>
     <t>Key</t>
   </si>
   <si>
@@ -230,6 +224,18 @@
   </si>
   <si>
     <t>Solve equation 1 and 2 to obtain crossover point</t>
+  </si>
+  <si>
+    <t>Rate of production, n_dot (parts/sec) =</t>
+  </si>
+  <si>
+    <t>If combined given, use this and ignore the 5 cells below</t>
+  </si>
+  <si>
+    <t>Combined running costs (£/sec) =</t>
+  </si>
+  <si>
+    <t>Extra: if capital/labour/energy is not ignored</t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -534,6 +540,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,20 +898,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59009D6D-5DCF-4633-8CF5-DEDA252EA24D}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="4" max="4" width="9.86328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="30.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.86328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.46484375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -912,7 +922,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="22"/>
       <c r="I1" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -923,120 +933,112 @@
     </row>
     <row r="2" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10">
+        <v>3</v>
+      </c>
+      <c r="B2" s="10" t="e">
         <f>((B3*B7)/(1-B6)) + (B8/B9)</f>
-        <v>100.4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="10">
+        <v>3</v>
+      </c>
+      <c r="J2" s="10" t="e">
         <f>((J3*J7)/(1-J6)) + (J8/J9)</f>
-        <v>200.22</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B3" s="6"/>
       <c r="D3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="12">
+        <v>19</v>
+      </c>
+      <c r="E3" s="12" t="e">
         <f>((B3*B7)/(1-B6))</f>
-        <v>0.4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" s="13">
         <f>B8</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J3" s="6"/>
       <c r="L3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="12">
+        <v>19</v>
+      </c>
+      <c r="M3" s="12" t="e">
         <f>((J3*J7)/(1-J6))</f>
-        <v>0.22000000000000003</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O3" s="13">
         <f>J8</f>
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0.01</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J4" s="4"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4">
         <f>B3+B4</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4">
         <f>J3+J4</f>
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4" t="e">
         <f>B4/B5</f>
-        <v>0.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
@@ -1044,12 +1046,12 @@
       <c r="I6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="4" t="e">
         <f>J4/J5</f>
-        <v>9.0909090909090912E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
@@ -1057,145 +1059,166 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B7" s="4"/>
       <c r="I7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="4">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4">
-        <v>10000</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B8" s="4"/>
       <c r="I8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="4">
-        <v>20000</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="4">
-        <v>100</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="I9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="4">
-        <v>100</v>
-      </c>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="11" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="8" t="e">
-        <f>((B3*B7)/(1-B6)) + (B8/B9) + (1/B13)*((B14/(B15*B16))+(B17))</f>
+      <c r="A11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="I11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="24"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="8" t="e">
+        <f>((B3*B7)/(1-B6)) + (B8/B9) + (1/B13)*(B14)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="8" t="e">
-        <f>((J3*J7)/(1-J6)) + (J8/J9) + (1/J13)*((J14/(J15*J16))+(J17))</f>
+      <c r="I12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="8" t="e">
+        <f>((J3*J7)/(1-J6)) + (J8/J9) + (1/J13)*(J14)</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="I12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4"/>
       <c r="I13" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B14" s="4"/>
+      <c r="C14" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="I14" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="I16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="4"/>
+      <c r="K14" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="16" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="26" t="e">
+        <f>((B3*B7)/(1-B6)) + (B8/B9) + (1/B13)*((B17/(B18*B19))+(B20))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="26" t="e">
+        <f>((J3*J7)/(1-J6)) + (J8/J9) + (1/J13)*((J17/(J18*J19))+(J20))</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B17" s="4"/>
       <c r="I17" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="19" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="16" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="I18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="I19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="I20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="22" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" s="18" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="18" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D6:G6"/>
   </mergeCells>

--- a/docs/Cost per unit calculation.xlsx
+++ b/docs/Cost per unit calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\QMUL Year 2 modules\Semester 2\EMS501U - Designing for Sustainable Manufacture\Exam Prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B025A23-D3CF-44B6-BB09-18FB29653CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C041054-29DD-4076-BA82-FC2A06A7EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B80BF410-154E-4A60-8685-422C7C147F4D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">'Cost per unit calc'!$B$2</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Cost per unit calc'!$B$10</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
   </definedNames>
@@ -232,10 +232,32 @@
     <t>If combined given, use this and ignore the 5 cells below</t>
   </si>
   <si>
-    <t>Combined running costs (£/sec) =</t>
-  </si>
-  <si>
     <t>Extra: if capital/labour/energy is not ignored</t>
+  </si>
+  <si>
+    <r>
+      <t>Combined running costs, C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (£/sec) =</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -298,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -406,62 +428,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -490,58 +460,143 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,6 +612,359 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>61233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>869171</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF27E4E-6E98-D8B5-C3E6-9168AB934A71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="246442"/>
+          <a:ext cx="3153407" cy="1330476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>102053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>31178</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>74839</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA9F128-5F15-4C13-C7D6-64305A2C35E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3224893"/>
+          <a:ext cx="3201642" cy="1442357"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>44167</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5A73A93-4435-3C75-463E-EA11C87D6341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5694591"/>
+          <a:ext cx="3313339" cy="778952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>34017</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>61232</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>18723</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01E0A3D-4157-4D64-8059-B65BE055DE77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7259410" y="244929"/>
+          <a:ext cx="3155170" cy="1319892"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13608</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>102053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>44786</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>74839</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1E3E0A-1F3E-4D40-BEC8-CBAA20283C53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7239001" y="3224893"/>
+          <a:ext cx="3201642" cy="1442357"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>20411</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>23755</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DC6210-E420-4B1E-B80E-409F109CAE01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7245804" y="5674179"/>
+          <a:ext cx="3313339" cy="778952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -898,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59009D6D-5DCF-4633-8CF5-DEDA252EA24D}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
@@ -909,319 +1317,340 @@
     <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.86328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.46484375" customWidth="1"/>
+    <col min="17" max="17" width="19.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="22"/>
-      <c r="I1" s="20" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="22"/>
-    </row>
-    <row r="2" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="10" t="e">
-        <f>((B3*B7)/(1-B6)) + (B8/B9)</f>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="16"/>
+    </row>
+    <row r="2" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5">
+        <f>((B11*B15)/(1-B14))</f>
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6">
+        <f>B16</f>
+        <v>200000</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="5" t="e">
+        <f>((J11*J15)/(1-J14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="10" t="e">
-        <f>((J3*J7)/(1-J6)) + (J8/J9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="D3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="12" t="e">
-        <f>((B3*B7)/(1-B6))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="N3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="13">
-        <f>B8</f>
+      <c r="O3" s="6">
+        <f>J16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="L3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="12" t="e">
-        <f>((J3*J7)/(1-J6))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="13">
-        <f>J8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4"/>
+      <c r="Q3" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="4"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="D6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="L6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+    </row>
+    <row r="9" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="10" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <f>((B11*B15)/(1-B14)) + (B16/B17)</f>
+        <v>2.41</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="e">
+        <f>((J11*J15)/(1-J14)) + (J16/J17)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22">
+        <f>0.2/40</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="22"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4">
-        <f>B3+B4</f>
+      <c r="B13" s="22">
+        <f>B11+B12</f>
+        <v>0.20500000000000002</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="22">
+        <f>J11+J12</f>
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4">
-        <f>J3+J4</f>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A14" s="23" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+      <c r="B14" s="22">
+        <f>B12/B13</f>
+        <v>2.4390243902439022E-2</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="e">
-        <f>B4/B5</f>
+      <c r="J14" s="22" t="e">
+        <f>J12/J13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="I6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="e">
-        <f>J4/J5</f>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A15" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="22">
+        <v>2</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="22"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A16" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="22">
+        <v>200000</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="25">
+        <v>100000</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="25"/>
+    </row>
+    <row r="26" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="27" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="I27" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3">
+        <f>((B11*B15)/(1-B14)) + (B16/B17) + (1/B29)*(B30)</f>
+        <v>2.4933333333333336</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J28" s="3" t="e">
+        <f>((J11*J15)/(1-J14)) + (J16/J17) + (1/J29)*(J30)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="I7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="I8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="I9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="11" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="23" t="s">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A29" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="22">
+        <f>40/60</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="22"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="I11" s="23" t="s">
+      <c r="B30" s="25">
+        <f>200/3600</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="24"/>
-    </row>
-    <row r="12" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="7" t="s">
+      <c r="J30" s="25"/>
+      <c r="K30" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="37" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="8" t="e">
-        <f>((B3*B7)/(1-B6)) + (B8/B9) + (1/B13)*(B14)</f>
+      <c r="B37" s="3" t="e">
+        <f>((B11*B15)/(1-B14)) + (B16/B17) + (1/B29)*((B38/(B39*B40))+(B41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="8" t="e">
-        <f>((J3*J7)/(1-J6)) + (J8/J9) + (1/J13)*(J14)</f>
+      <c r="J37" s="3" t="e">
+        <f>((J11*J15)/(1-J14)) + (J16/J17) + (1/J29)*((J38/(J39*J40))+(J41))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="I13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="16" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="26" t="e">
-        <f>((B3*B7)/(1-B6)) + (B8/B9) + (1/B13)*((B17/(B18*B19))+(B20))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="26" t="e">
-        <f>((J3*J7)/(1-J6)) + (J8/J9) + (1/J13)*((J17/(J18*J19))+(J20))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" s="3" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A38" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="I17" s="3" t="s">
+      <c r="B38" s="20"/>
+      <c r="I38" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" s="3" t="s">
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="I18" s="3" t="s">
+      <c r="B39" s="22"/>
+      <c r="I39" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
+      <c r="J39" s="22"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A40" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="I19" s="3" t="s">
+      <c r="B40" s="22"/>
+      <c r="I40" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
+      <c r="J40" s="22"/>
+    </row>
+    <row r="41" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="I20" s="3" t="s">
+      <c r="B41" s="25"/>
+      <c r="I41" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="22" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A24" s="18" t="s">
-        <v>15</v>
-      </c>
+      <c r="J41" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="I27:J27"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Cost per unit calculation.xlsx
+++ b/docs/Cost per unit calculation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\QMUL Year 2 modules\Semester 2\EMS501U - Designing for Sustainable Manufacture\Exam Prep\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\Final Couch to Coder 2024 website\yashv432.github.io\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C041054-29DD-4076-BA82-FC2A06A7EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D92A35-532D-44A8-9120-0A103D34ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B80BF410-154E-4A60-8685-422C7C147F4D}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t xml:space="preserve">Scrap fraction, f = </t>
   </si>
@@ -264,7 +264,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +289,22 @@
     <font>
       <sz val="8"/>
       <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -553,7 +569,6 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -572,6 +587,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -584,19 +606,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,8 +724,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3224893"/>
-          <a:ext cx="3201642" cy="1442357"/>
+          <a:off x="0" y="3250596"/>
+          <a:ext cx="3197359" cy="1454452"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1321,66 +1337,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-      <c r="I1" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="22"/>
+      <c r="I1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="16"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="22"/>
     </row>
     <row r="2" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4" t="e">
         <f>((B11*B15)/(1-B14))</f>
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="F3" s="5" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f>B16</f>
-        <v>200000</v>
-      </c>
-      <c r="L3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="5" t="e">
+      <c r="M3" s="4" t="e">
         <f>((J11*J15)/(1-J14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <f>J16</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1388,258 +1404,321 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="L6" s="13" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="L6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="9" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="10" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2" t="e">
         <f>((B11*B15)/(1-B14)) + (B16/B17)</f>
-        <v>2.41</v>
-      </c>
-      <c r="I10" s="2" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="3" t="e">
+      <c r="J10" s="2" t="e">
         <f>((J11*J15)/(1-J14)) + (J16/J17)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="I11" s="19" t="s">
+      <c r="B11" s="13"/>
+      <c r="I11" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="22">
-        <f>0.2/40</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="I12" s="21" t="s">
+      <c r="B12" s="15"/>
+      <c r="I12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="22"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="15">
         <f>B11+B12</f>
-        <v>0.20500000000000002</v>
-      </c>
-      <c r="I13" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="15">
         <f>J11+J12</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="15" t="e">
         <f>B12/B13</f>
-        <v>2.4390243902439022E-2</v>
-      </c>
-      <c r="I14" s="23" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="J14" s="22" t="e">
+      <c r="J14" s="15" t="e">
         <f>J12/J13</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="22">
-        <v>2</v>
-      </c>
-      <c r="I15" s="21" t="s">
+      <c r="B15" s="15"/>
+      <c r="I15" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="22"/>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="22">
-        <v>200000</v>
-      </c>
-      <c r="I16" s="21" t="s">
+      <c r="B16" s="15"/>
+      <c r="I16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="22"/>
-    </row>
-    <row r="17" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="24" t="s">
+      <c r="J16" s="15"/>
+    </row>
+    <row r="17" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="25">
-        <v>100000</v>
-      </c>
-      <c r="I17" s="24" t="s">
+      <c r="B17" s="18"/>
+      <c r="I17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="25"/>
-    </row>
-    <row r="26" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="27" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="17" t="s">
+      <c r="J17" s="18"/>
+    </row>
+    <row r="26" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="27" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="I27" s="17" t="s">
+      <c r="B27" s="24"/>
+      <c r="I27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="2" t="s">
+      <c r="J27" s="24"/>
+      <c r="L27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="4" t="e">
+        <f>((J10*J14)/(1-J13)) + ((1/J28)*(J29))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="5">
+        <f>J40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2" t="e">
         <f>((B11*B15)/(1-B14)) + (B16/B17) + (1/B29)*(B30)</f>
-        <v>2.4933333333333336</v>
-      </c>
-      <c r="I28" s="2" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="4" t="e">
+        <f>((B11*B15)/(1-B14)) + ((1/B29)*(B30))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="5">
+        <f>B41</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J28" s="3" t="e">
+      <c r="J28" s="2" t="e">
         <f>((J11*J15)/(1-J14)) + (J16/J17) + (1/J29)*(J30)</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A29" s="21" t="s">
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A29" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="22">
-        <f>40/60</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="I29" s="21" t="s">
+      <c r="B29" s="15"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="22"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="24" t="s">
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="25">
-        <f>200/3600</f>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="18"/>
+      <c r="C30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="24" t="s">
+      <c r="I30" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J30" s="25"/>
-      <c r="K30" s="12" t="s">
+      <c r="J30" s="18"/>
+      <c r="K30" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="37" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="2" t="s">
+    <row r="36" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="37" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="3" t="e">
+      <c r="B37" s="2" t="e">
         <f>((B11*B15)/(1-B14)) + (B16/B17) + (1/B29)*((B38/(B39*B40))+(B41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J37" s="3" t="e">
+      <c r="J37" s="2" t="e">
         <f>((J11*J15)/(1-J14)) + (J16/J17) + (1/J29)*((J38/(J39*J40))+(J41))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A38" s="19" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A38" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="I38" s="19" t="s">
+      <c r="B38" s="13"/>
+      <c r="D38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="4" t="e">
+        <f>((B11*B15)/(1-B14)) + ((1/B29)*((B38/(B39*B40))+B41))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="5">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J38" s="20"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A39" s="21" t="s">
+      <c r="J38" s="13"/>
+      <c r="L38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="4" t="e">
+        <f>((J11*J15)/(1-J14)) + ((1/J29)*((J38/(J39*J40))+J41))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" s="5">
+        <f>J50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A39" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="I39" s="21" t="s">
+      <c r="B39" s="15"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J39" s="22"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A40" s="21" t="s">
+      <c r="J39" s="15"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A40" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="I40" s="21" t="s">
+      <c r="B40" s="15"/>
+      <c r="I40" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J40" s="22"/>
-    </row>
-    <row r="41" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="24" t="s">
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="I41" s="24" t="s">
+      <c r="B41" s="18"/>
+      <c r="I41" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J41" s="25"/>
+      <c r="J41" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1651,6 +1730,7 @@
     <mergeCell ref="D6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/Cost per unit calculation.xlsx
+++ b/docs/Cost per unit calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yashv\Downloads\Final Couch to Coder 2024 website\yashv432.github.io\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D92A35-532D-44A8-9120-0A103D34ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{790FE43F-0D92-4026-897E-CFD9D28FDE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B80BF410-154E-4A60-8685-422C7C147F4D}"/>
   </bookViews>
@@ -594,6 +594,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -606,13 +613,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1337,24 +1337,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="22"/>
-      <c r="I1" s="20" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25"/>
+      <c r="I1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="22"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D2" s="3" t="s">
@@ -1418,29 +1418,29 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="L6" s="19" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="L6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="9" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="10" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="e">
         <f>((B11*B15)/(1-B14)) + (B16/B17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="J10" s="2" t="e">
@@ -1532,31 +1532,17 @@
     </row>
     <row r="26" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="27" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="I27" s="23" t="s">
+      <c r="B27" s="21"/>
+      <c r="I27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="24"/>
-      <c r="L27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="4" t="e">
-        <f>((J10*J14)/(1-J13)) + ((1/J28)*(J29))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="5">
-        <f>J40</f>
-        <v>0</v>
-      </c>
+      <c r="J27" s="21"/>
     </row>
     <row r="28" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B28" s="2" t="e">
@@ -1574,21 +1560,29 @@
         <v>20</v>
       </c>
       <c r="G28" s="5">
-        <f>B41</f>
+        <f>B16</f>
         <v>0</v>
       </c>
-      <c r="I28" s="25" t="s">
+      <c r="I28" s="19" t="s">
         <v>4</v>
       </c>
       <c r="J28" s="2" t="e">
         <f>((J11*J15)/(1-J14)) + (J16/J17) + (1/J29)*(J30)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="6" t="s">
-        <v>18</v>
+      <c r="L28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="4" t="e">
+        <f>((J11*J15)/(1-J14)) + ((1/J29)*(J30))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="5">
+        <f>J16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.45">
@@ -1606,6 +1600,12 @@
         <v>24</v>
       </c>
       <c r="J29" s="15"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="17" t="s">
@@ -1625,14 +1625,14 @@
     </row>
     <row r="36" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="37" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="2" t="e">
         <f>((B11*B15)/(1-B14)) + (B16/B17) + (1/B29)*((B38/(B39*B40))+(B41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I37" s="25" t="s">
+      <c r="I37" s="19" t="s">
         <v>4</v>
       </c>
       <c r="J37" s="2" t="e">
@@ -1656,7 +1656,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="5">
-        <f>B50</f>
+        <f>B16</f>
         <v>0</v>
       </c>
       <c r="I38" s="12" t="s">
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="O38" s="5">
-        <f>J50</f>
+        <f>J16</f>
         <v>0</v>
       </c>
     </row>
